--- a/survey_templates/043_fun_group_dynamics_survey--survey_templates.xlsx
+++ b/survey_templates/043_fun_group_dynamics_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,8 +746,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,12 +775,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small_team'}</t>
+          <t>small_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small Team'}</t>
+          <t>Small Team</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium_team'}</t>
+          <t>medium_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium Team'}</t>
+          <t>Medium Team</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large_team'}</t>
+          <t>large_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large Team'}</t>
+          <t>Large Team</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'direct_and_clear'}</t>
+          <t>direct_and_clear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Direct and Clear'}</t>
+          <t>Direct and Clear</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'indirect_and_clear'}</t>
+          <t>indirect_and_clear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Indirect and Clear'}</t>
+          <t>Indirect and Clear</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'direct_and_vague'}</t>
+          <t>direct_and_vague</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Direct and Vague'}</t>
+          <t>Direct and Vague</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'indirect_and_vague'}</t>
+          <t>indirect_and_vague</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Indirect and Vague'}</t>
+          <t>Indirect and Vague</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'almost_never'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Almost Never'}</t>
+          <t>Almost Never</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'celebrating_successes'}</t>
+          <t>celebrating_successes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Celebrating Successes'}</t>
+          <t>Celebrating Successes</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'playing_games'}</t>
+          <t>playing_games</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Playing Games'}</t>
+          <t>Playing Games</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_lunches'}</t>
+          <t>team_lunches</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Lunches'}</t>
+          <t>Team Lunches</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'team_challenges'}</t>
+          <t>team_challenges</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Team Challenges'}</t>
+          <t>Team Challenges</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
